--- a/important_mails_2026-05-02.xlsx
+++ b/important_mails_2026-05-02.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H173"/>
+  <dimension ref="A1:H175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Sat, 2 May 2026 02:13:49 +0000</t>
+          <t>Sat, 2 May 2026 13:15:01 +0000</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -515,6 +515,56 @@
       </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Submit product safety documentation to reactivate listings
+ Hello Weihai EU,
+ Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
+ Why is this happening?
+ We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
+ The table at the end of this email provides product-specific compliance requirements.
+ How do I reactivate my listings?
+ To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
+-
+ If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
+-
+ If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 2 May 2026 02:13:49 +0000</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Submit product safety documentation to reactivate listings</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -532,40 +582,98 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 2 May 2026 15:27:47 +0600</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Review Deals &lt;amazonreviewsdeals1@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Review Rating Deals</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Not getting sales on Amazon? Even after doing everything right? Then this
+message is for you!
+Have you properly created your Amazon seller account, selected a good
+product, used strong keywords - yet still getting very low sales?
+ The problem is simple — your product lacks trustworthy reviews and ratings!
+Today’s customers check reviews first, then decide to buy.without strong
+reviews—sales won’t come.
+ That’s where we come in!
+We have Amazon Top Reviewers + Vine Buyers from Germany 🇩🇪, Spain 🇪🇸,
+Italy 🇮🇹, USA 🇺🇸, UK 🇬🇧, Canada 🇨🇦, and France 🇫🇷.
+✅ What we offer:
+⭐ 5-Star Text Reviews
+📸 5-Star Photo Reviews
+🎥 5-Star Video Reviews
+👉 All from real and authentic buyers!
+If you are satisfied with the review rating, you will provide a full refund
+to the buyer. For each review, you will also pay me a commission.
+✨ We manage your feedback, handle your reviews, and take your business to
+the next level!
+📩 Interested? Contact us now!
+👇 +1 (778) 721-5486</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 03:15:52 +0000</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -581,40 +689,40 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 02:15:51 +0000</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -630,39 +738,39 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 02:15:45 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -678,39 +786,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 01:23:15 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -726,39 +834,39 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 04:46:00 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -782,39 +890,39 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 07:28:26 +0000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (5NT+O11io4)</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -834,39 +942,39 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 23:31:40 +0000</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -886,39 +994,39 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:27:01 +0000</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -935,39 +1043,39 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:26:48 +0000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -987,39 +1095,39 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 17:03:06 +0000</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1039,39 +1147,39 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Sun, 26 Apr 2026 14:08:56 +0000</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1088,39 +1196,39 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Sun, 26 Apr 2026 14:08:50 +0000</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1140,39 +1248,39 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:19:29 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1190,39 +1298,39 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 12:52:07 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -1238,39 +1346,39 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 02:11:27 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1288,39 +1396,39 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 14:14:16 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1338,39 +1446,39 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 13:03:36 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility 96
  Complete Pan EU enrollment: Add NL products now
@@ -1380,39 +1488,39 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 09:05:17 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>【请勿回复此日志，如有问题请加入下方邮件中的企微群】
 卖家您好，
@@ -1433,39 +1541,39 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:13:11 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -1481,39 +1589,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:52:19 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -1532,39 +1640,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 03:13:33 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;merch.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20093870001] Other account issues</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>Hello from Amazon Selling Partner Support,
 My name is Ritam. I am a Live Channel Specialist and I'm contacting you to follow up on your concern regarding the reinstatement of your listing B0FCDRNTT8.
@@ -1575,39 +1683,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 15:09:15 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -1623,39 +1731,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:16:19 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -1669,39 +1777,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 02:33:13 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Transparency Invoice/Credit note for 04/2026</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>96
  Dear Customer,
@@ -1719,40 +1827,40 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 02:13:34 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -1768,39 +1876,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 02:13:30 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -1816,39 +1924,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 01:21:43 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -1864,40 +1972,40 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 01:18:50 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -1913,39 +2021,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 21:55:17 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>规划您的 La French Week 促销活动</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -1962,39 +2070,39 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 21:32:46 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩
 尊敬的卖家，
@@ -2023,39 +2131,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 15:08:42 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -2071,39 +2179,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 14:12:49 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -2117,39 +2225,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 14:07:32 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -2164,39 +2272,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 10:18:53 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -2216,39 +2324,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 20:59:56 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Tus límites de capacidad de Logística de Amazon para mayo</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>96
  Tus límites de capacidad de Logística de Amazon para mayo
@@ -2277,40 +2385,40 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 14:37:52 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Il team di Gestione multicanale &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Aggiornamenti ai costi di Gestione multicanale in vigore dal 29
  maggio 2026</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>96
  Stiamo aggiornando le tariffe di Gestione multicanale per aiutarti a ridurre i costi e investire nella crescita della tua attività.
@@ -2323,39 +2431,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 14:30:37 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>The Multichannel Fulfillment team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>MCF fee updates effective May 29, 2026</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  We’re updating our Multichannel Fulfillment fees to help you reduce your costs so you can invest in growing your business.
@@ -2370,39 +2478,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 14:25:56 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>El Departamento de Logística Multicanal &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Actualización de las tarifas de Logística Multicanal en vigor a partir del 29 de mayo de 2026</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>96
  Vamos a actualizar nuestras tarifas de Logística Multicanal para ayudarte a reducir los costes y así puedas invertir en hacer crecer tu negocio.
@@ -2415,40 +2523,40 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:38:42 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Presenta documentos de cumplimiento normativo del producto para
  evitar que se retiren los listings</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta documentos de cumplimiento normativo del producto para evitar que se retiren los listings
@@ -2463,40 +2571,40 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:25:34 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Documenten over productconformiteit indienen om verwijdering van
  productvermeldingen te voorkomen</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>96
  Documenten over productconformiteit indienen om verwijdering van productvermeldingen te voorkomen
@@ -2510,39 +2618,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:06:50 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Prześlij dokumenty zgodności dotyczące produktu, aby zapobiec usunięciu oferty</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Prześlij dokumenty zgodności dotyczące produktu, aby zapobiec usunięciu oferty
@@ -2556,39 +2664,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:58:32 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Skicka in dokument om produktöverensstämmelse för att undvika att produktposter tas bort</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in dokument om produktöverensstämmelse för att undvika att produktposter tas bort
@@ -2603,39 +2711,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:54:06 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione di conformità dei prodotti per evitare la rimozione delle offerte</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione di conformità dei prodotti per evitare la rimozione delle offerte
@@ -2649,39 +2757,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:50:08 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Soumettez les documents de conformité des produits pour éviter le retrait de la mise en vente</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettez les documents de conformité des produits pour éviter le retrait de la mise en vente
@@ -2696,39 +2804,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 15:58:40 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -2743,39 +2851,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Mon, 27 Apr 2026 05:22:10 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -2794,39 +2902,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Sun, 26 Apr 2026 11:10:42 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -2842,39 +2950,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 00:16:37 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>View your US Q2-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q2-2026
@@ -2904,39 +3012,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 18:05:15 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>提交商品合规文件，以避免商品被移除</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>96
  提交商品合规文件，以避免商品被移除
@@ -2985,39 +3093,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 14:54:23 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $44.85 in an attempt to settle your Amazon seller account balance.
@@ -3033,39 +3141,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 04:59:05 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (26041219YV)</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3085,39 +3193,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 02:11:54 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (W4mGNrNTVu)</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -3143,39 +3251,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 15:50:12 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3196,39 +3304,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:11:54 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (pVfzD86piw)</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -3254,39 +3362,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Apr 2026 05:12:21 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;seller-notification@amazon.ie&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Outstanding balance on your Amazon account</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>Hello,
  You have an outstanding balance on your account in the amount of 7,79 EUR. We will debit this amount from the credit card (Visa) that you registered as the charge method for your account.
@@ -3300,39 +3408,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 15:01:26 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3352,39 +3460,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 14:27:43 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3401,39 +3509,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 14:45:45 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -3449,39 +3557,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 14:44:32 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3501,39 +3609,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Apr 2026 15:38:30 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3550,39 +3658,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Mon, 13 Apr 2026 16:26:54 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;amazon_te@amazon.fr&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Paiement du solde de votre compte de paiement Vendre sur Amazon</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>Cher vendeur,
  Nous avons débité votre carte bancaire (Visa) pour un montant de 242,36 EUR pour le règlement du solde de votre compte de paiement Vendre sur Amazon.
@@ -3594,39 +3702,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Mon, 13 Apr 2026 15:24:52 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Negative balance adjustment across your Selling on Amazon accounts</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3649,39 +3757,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Sat, 11 Apr 2026 15:29:23 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Rettifica del saldo negativo nei tuoi account</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3705,39 +3813,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 14:28:35 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on Your Selling on Amazon payment account</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
  We have charged your (Visa) credit card for 62.05 in an attempt to settle your account balance.
@@ -3752,39 +3860,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 15:16:38 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.pl&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Nieuregulowane saldo na koncie Amazon</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>Witamy!
  Masz na swoim koncie nieuregulowane saldo w wysokośc PLN 45.29. Obciążymy tą kwotą kartę kredytową zarejestrowaną jako metoda płatności dla Twojego konta
@@ -3798,40 +3906,40 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:54:29 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Refunds for digital services fees related to the Canadian DST will
  begin on April 15</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>96
  We’ll refund digital services fees and the taxes on those fees related to the Canadian digital services tax that we had charged from September 1, 2024, through August 15, 2025.
@@ -3848,39 +3956,39 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 13:38:25 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3900,39 +4008,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 15:38:29 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3949,39 +4057,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Apr 2026 17:15:23 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -4000,39 +4108,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:15:37 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -4051,39 +4159,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:09:18 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -4102,39 +4210,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Apr 2026 03:03:00 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 You recently received a notice about the removal of your listing(s) for the product(s) listed below.
@@ -4154,39 +4262,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Apr 2026 01:27:00 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;merch.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20061337331] 对危险品分类提出异议</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家/供应商:您好!
 我们了解到您希望重新激活商品 ASIN: B0FCDRNTT8。
@@ -4215,39 +4323,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 10:07:05 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -4265,39 +4373,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:15:48 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4315,39 +4423,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:08:57 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4365,39 +4473,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 06:10:23 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>"compliance-ops-mass-programs@amazon.com" &lt;compliance-ops-mass-programs@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12449434352] 【邀请函】诚邀您参与亚马逊卖家合规策略调研</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>尊敬的销售伙伴，
 您好！
@@ -4411,39 +4519,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 21:09:24 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4461,40 +4569,40 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 14:16:35 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE:
  A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -4511,40 +4619,40 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 09:57:17 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -4561,39 +4669,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 16:06:35 +0800 (GMT+08:00)</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>苏浩然 &lt;suhr@cvc.org.cn&gt;</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Amazon DV TIC</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家，您好。
 我们可以为您提供亚马逊DV验证报告服务。
@@ -4627,39 +4735,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 10:14:18 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -4674,39 +4782,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 03:38:27 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are contacting you to let you know that you could be missing out on sales opportunities because of your incomplete listings.
@@ -4722,39 +4830,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Fri, 17 Apr 2026 11:22:53 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>"pc-eu-sesu-seller-compliance@amazon.com" &lt;pc-eu-sesu-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 11569978862] 【需立即行动】请通过亚马逊认可的TIC服务商完成儿童玩具合规</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 我们紧急通知您，您在【欧洲】站点的部分【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】或【已通过】。
@@ -4778,39 +4886,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Apr 2026 17:53:23 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -4829,39 +4937,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 09:10:03 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -4877,39 +4985,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 07:35:31 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>Seller Assistant now available in the UK</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>Seller Assistant now available in the UK
 [Amazon logo](https://go.amazonsellerservices.com/e/229492/-ld-EMUSSMX-PD25/7z2r9lq/6605548725/h/3xRPn8Yyq31Jz0Gqi8FK51O58vBJkaDT5nhLB1ousbA)
@@ -4921,39 +5029,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 06:23:28 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 You recently received a notice about the removal of your listing(s) for the product(s) listed below.
@@ -4973,39 +5081,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Sun, 12 Apr 2026 09:09:25 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -5023,40 +5131,40 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 15:28:03 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -5074,39 +5182,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 12:03:53 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Reactivate your EU listings - GPSR compliance required</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Reactivate your EU listings - GPSR compliance required
@@ -5126,39 +5234,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 10:50:30 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>EU and UK Compliance Brief</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe
  96
@@ -5179,39 +5287,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 10:38:53 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>EU and UK Compliance Brief</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe
  96
@@ -5232,40 +5340,40 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 10:23:33 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>The Amazon Europe team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>VAT Calculation Services will calculate VAT by shipment as of June
  1</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>96
  New tax calculation method ensures compliance with European e-invoicing mandates.
@@ -5281,39 +5389,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 04:56:03 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>【请勿回复】
 尊敬的销售合作伙伴，
@@ -5336,39 +5444,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:19:17 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -5386,39 +5494,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:18:50 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -5436,39 +5544,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Apr 2026 05:38:32 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -5489,39 +5597,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:19:11 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -5539,40 +5647,40 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:18:24 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om de deactivering van de
  productvermelding te voorkomen</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -5590,39 +5698,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:15:32 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -5639,39 +5747,39 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:12:50 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -5689,40 +5797,40 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:12:30 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per evitare la
  disattivazione dell'offerta</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -5740,39 +5848,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:09:22 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour éviter la désactivation des mises en vente</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>96
  Bonjour Weihai EU,
@@ -5790,39 +5898,39 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 00:31:36 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>规划您的 La French Week 促销活动</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -5839,39 +5947,39 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Apr 2026 15:00:54 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5886,39 +5994,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Apr 2026 07:42:42 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Act today &amp; improve Sales on Excess Inventory</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5937,39 +6045,39 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:32:20 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Prime Day：立即提报您的促销</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>Prime Day（日期待公布）：立即提报您的促销
 尊敬的卖家，
@@ -5987,39 +6095,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:19:47 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以重新启售商品</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>96
  提交商品安全文件以重新启售商品
@@ -6058,39 +6166,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:17:42 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -6106,40 +6214,40 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:17:14 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -6155,39 +6263,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:13:36 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -6203,39 +6311,39 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:13:34 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -6249,40 +6357,40 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:11:30 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -6298,39 +6406,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:09:39 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -6346,39 +6454,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 05:22:42 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -6399,39 +6507,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 15:14:51 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -6446,39 +6554,39 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Fri, 17 Apr 2026 09:39:52 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Verify your primary operating address for tax purposes</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Amazon Services
  Verify your primary operating address for tax purposes
@@ -6495,39 +6603,39 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Apr 2026 15:10:49 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>[Formal Notice – Immediate Action Required] Review and certify your business information within 10 days to avoid account deactivation</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -6541,39 +6649,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 17:59:02 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>Amazon Verkaeuferservice &lt;merch.service05@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12354633592] 其他账户问题</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>尊敬的销售伙伴：
 您好！
@@ -6592,40 +6700,40 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 17:22:14 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>Amazon Product Support Team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>Reduce Returns &amp; Boost Customer Satisfaction - Enrol in Amazon
  Product Support</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>96
  Enrol now into Amazon Product Support !
@@ -6639,40 +6747,40 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 13:44:27 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Reactiva tus listings en la UE: se requiere el cumplimiento del
  Reglamento relativo a la seguridad general de los productos</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>96
  Reactiva tus listings en la UE: se requiere el cumplimiento del Reglamento relativo a la seguridad general de los productos
@@ -6690,39 +6798,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 01:52:13 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Re: 🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 Just a short follow-up regarding the [Vergleich.org](http://Vergleich.org)
@@ -6755,39 +6863,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 17:17:52 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>Introducing Global Warehousing &amp; Distribution</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>96
  Store inventory at origin in China with lower costs and faster speeds.
@@ -6802,39 +6910,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 16:27:24 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 3/2026 (Votre Facture Expédié Par Amazon Amazon.ca pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -6853,39 +6961,39 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 11:49:51 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>96
  Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti
@@ -6904,39 +7012,39 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 10:53:45 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>Las tarifas por puesta de inventario a disposición de Amazon y retirada de Logística de Amazon se cobrarán a medida que se procesen las unidades</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>96
  Las tarifas por retirada y puesta de inventario a disposición de Amazon de Logística de Amazon se cobrarán ahora por unidad en el momento en que cada unidad se retire o se ponga a nuestra disposición.
@@ -6948,39 +7056,39 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 09:19:33 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>Opłaty za usunięcie i likwidację zapasów FBA naliczane podczas przetwarzania jednostek</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>96
  Opłaty za wycofanie i usunięcie zapasów w ramach FBA będą teraz pobierane od każdej jednostki w momencie jej wycofania lub usunięcia.
@@ -6996,39 +7104,39 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 08:46:52 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>Addebito delle tariffe di rimozione e per reimpiego quando le unità vengono elaborate</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>96
  Le tariffe per gli ordini di rimozione e di reimpiego di inventario di Logistica di Amazon verranno ora addebitate per unità ogni volta che un'unità viene rimossa o destinata ad altro uso.
@@ -7040,39 +7148,39 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 15:00:43 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -7087,39 +7195,39 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 01:13:24 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Verkäufer von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Verkäufer für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -7131,39 +7239,39 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 00:28:23 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>Je Creditnota Verkoper Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Creditnota Verkoper voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -7175,39 +7283,39 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 23:40:40 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -7219,39 +7327,39 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:17:10 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -7263,39 +7371,39 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:08:24 +0000</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -7307,39 +7415,39 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:03:23 +0000</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 3/2026</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -7351,39 +7459,39 @@
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 21:18:12 +0000</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -7395,39 +7503,39 @@
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:40:48 +0000</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 3/2026</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 3/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -7439,39 +7547,39 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:23:05 +0000</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -7483,39 +7591,39 @@
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:10:52 +0000</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 3/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -7534,39 +7642,39 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:00:59 +0000</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -7578,39 +7686,39 @@
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 19:23:08 +0000</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Selbstfakturierung AGL von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Selbstfakturierung AGL für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -7622,39 +7730,39 @@
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 18:31:47 +0000</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 3/2026</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic AGL Merchant Self-Billing Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -7666,39 +7774,39 @@
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:54:15 +0000</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Säljare Amazon.se för 3/2026</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Säljare för månaden 3/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -7710,39 +7818,39 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:52:00 +0000</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -7754,39 +7862,39 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:39:20 +0000</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 3/2026</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -7798,39 +7906,39 @@
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:07:04 +0000</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 3/2026</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 3/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -7842,39 +7950,39 @@
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:06:30 +0000</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 3/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -7893,39 +8001,39 @@
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 15:55:59 +0000</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr"/>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -7937,40 +8045,40 @@
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 15:00:18 +0000</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.com.be voor 3/2026 (Votre Facture
  Vendeur Amazon.com.be pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -7989,39 +8097,39 @@
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 14:50:20 +0000</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Verkäufer von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr"/>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Verkäufer für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -8033,39 +8141,39 @@
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 14:43:40 +0000</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.sa Merchant Invoice for 3/2026 (Amazon.sa فاتورة ضريبة القيمة المضافة (VAT) الخاصة بالتاجر الخاصة بك لشهر 3/2026)</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr"/>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -8084,39 +8192,39 @@
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>Mon, 06 Apr 2026 01:10:45 +0000</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Re: 🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr"/>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 I wanted to briefly follow up regarding the Vergleich.org award for your
@@ -8148,39 +8256,39 @@
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 15:20:39 +0000</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12317833332] 其他账户问题</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr"/>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家/供应商：您好！
 关于您 ASIN B0CSGBZG8W 购物车的问题，经过审核，我们发现该商品的价格不符合成为推荐商品的条件，因为它似乎过高。
@@ -8207,39 +8315,39 @@
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 09:59:13 +0000</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>&lt;p&gt;Grazie per aver creato un nuovo caso: -- 12317833332&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr"/>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr"/>
+      <c r="H159" s="2" t="inlineStr">
         <is>
           <t>La ringraziamo per aver contattato il Supporto al venditore di Amazon.
 Abbiamo aperto un caso riguardo al suo problema. Un membro del nostro team la contatterà appena possibile. Rispondiamo alla maggior parte delle e-mail entro 12 ore.
@@ -8251,39 +8359,39 @@
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 14:57:25 +0000</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>Recargo relacionado con combustible y gastos de logística: Logística de Amazon y Logística Multicanal en la UE</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr"/>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t>96
  A partir del 17 de abril de 2026, se aplicará un recargo por combustible y gastos de logística del 1,5 % a las tarifas de gestión logística de Logística de Amazon. En el caso de Logística Multicanal, este recargo entrará en vigor el 2 de mayo de 2026.
@@ -8293,39 +8401,39 @@
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 14:01:37 +0000</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F161" s="2" t="inlineStr">
         <is>
           <t>Dopłata z tytułu kosztów paliwa i logistyki: usługi FBA i MFC w UE</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr"/>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr"/>
+      <c r="H161" s="2" t="inlineStr">
         <is>
           <t>96
  Od 17 kwietnia 2026 r. do opłat za realizację w programie „Realizacja przez Amazon” (FBA) zaczynamy doliczać dopłatę w wysokości 1,5% z tytułu kosztów paliwa i logistyki. W przypadku usługi „Realizacja wielokanałowa” (MCF) dopłata ta będzie miała zastosowanie od 2 maja 2026 r.
@@ -8335,39 +8443,39 @@
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Apr 2026 04:25:43 +0000</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr"/>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr"/>
+      <c r="H162" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -8391,39 +8499,39 @@
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Apr 2026 03:35:07 +0000</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F161" s="2" t="inlineStr">
+      <c r="F163" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-05-07</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr"/>
-      <c r="H161" s="2" t="inlineStr">
+      <c r="G163" s="2" t="inlineStr"/>
+      <c r="H163" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -8444,39 +8552,39 @@
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 04:00:50 +0000</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F162" s="2" t="inlineStr">
+      <c r="F164" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-30</t>
         </is>
       </c>
-      <c r="G162" s="2" t="inlineStr"/>
-      <c r="H162" s="2" t="inlineStr">
+      <c r="G164" s="2" t="inlineStr"/>
+      <c r="H164" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -8498,39 +8606,39 @@
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="inlineStr">
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 03:30:46 +0000</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F163" s="2" t="inlineStr">
+      <c r="F165" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr"/>
-      <c r="H163" s="2" t="inlineStr">
+      <c r="G165" s="2" t="inlineStr"/>
+      <c r="H165" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -8553,39 +8661,39 @@
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 18:58:06 +0000</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F164" s="2" t="inlineStr">
+      <c r="F166" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-23</t>
         </is>
       </c>
-      <c r="G164" s="2" t="inlineStr"/>
-      <c r="H164" s="2" t="inlineStr">
+      <c r="G166" s="2" t="inlineStr"/>
+      <c r="H166" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -8606,39 +8714,39 @@
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="inlineStr">
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 18:27:29 +0000</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="E167" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F165" s="2" t="inlineStr">
+      <c r="F167" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G165" s="2" t="inlineStr"/>
-      <c r="H165" s="2" t="inlineStr">
+      <c r="G167" s="2" t="inlineStr"/>
+      <c r="H167" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -8661,39 +8769,39 @@
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:48:38 +0000</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="E168" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F166" s="2" t="inlineStr">
+      <c r="F168" s="2" t="inlineStr">
         <is>
           <t>Remove aged, stranded and unfulfillable inventory by April 30</t>
         </is>
       </c>
-      <c r="G166" s="2" t="inlineStr"/>
-      <c r="H166" s="2" t="inlineStr">
+      <c r="G168" s="2" t="inlineStr"/>
+      <c r="H168" s="2" t="inlineStr">
         <is>
           <t>96
  Take action now to avoid automatic removal of your Fulfilment by Amazon inventory.
@@ -8706,39 +8814,39 @@
         </is>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="inlineStr">
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 11:41:39 +0800 (GMT+08:00)</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>GTTC国际业务部玩具组 &lt;gttctoy@cngttc.cn&gt;</t>
         </is>
       </c>
-      <c r="F167" s="2" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
         <is>
           <t>AMAZON DV TIC TRF ID--Top urgently</t>
         </is>
       </c>
-      <c r="G167" s="2" t="inlineStr"/>
-      <c r="H167" s="2" t="inlineStr">
+      <c r="G169" s="2" t="inlineStr"/>
+      <c r="H169" s="2" t="inlineStr">
         <is>
           <t>Dear Vendor,        Some of your TR numbers on Amazon have been pending in our backend for a long time without timely processing. We plan to automatically clear all unresponded TR numbers in our system two days later.
 If you have any TR numbers that require sample submission for testing, please reply to this email and send us the corresponding TR numbers within two days, and contact our relevant customer service within one week to arrange sample submission.
@@ -8747,39 +8855,39 @@
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="2" t="inlineStr">
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D168" s="2" t="inlineStr">
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
         <is>
           <t>Fri, 17 Apr 2026 02:18:44 +0000</t>
         </is>
       </c>
-      <c r="E168" s="2" t="inlineStr">
+      <c r="E170" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F168" s="2" t="inlineStr">
+      <c r="F170" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G168" s="2" t="inlineStr"/>
-      <c r="H168" s="2" t="inlineStr">
+      <c r="G170" s="2" t="inlineStr"/>
+      <c r="H170" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
@@ -8795,39 +8903,39 @@
         </is>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 14:20:37 +0000</t>
         </is>
       </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
         <is>
           <t>Get discounts up to €500 per shipment by expanding to Europe!</t>
         </is>
       </c>
-      <c r="G169" s="2" t="inlineStr"/>
-      <c r="H169" s="2" t="inlineStr">
+      <c r="G171" s="2" t="inlineStr"/>
+      <c r="H171" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/-logo/7z2qvdy/6598918207/h/oQJ3hcZAc232rnIjbHrMLH2dvtBVfEq_dAzSA60S8Es)
 C2S2 PCP Pallet Limited Time Promotion
@@ -8843,39 +8951,39 @@
         </is>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" s="2" t="inlineStr">
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C170" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D170" s="2" t="inlineStr">
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 11:27:28 +0000</t>
         </is>
       </c>
-      <c r="E170" s="2" t="inlineStr">
+      <c r="E172" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F170" s="2" t="inlineStr">
+      <c r="F172" s="2" t="inlineStr">
         <is>
           <t>FBA removal and disposal fees to be charged as units are processed</t>
         </is>
       </c>
-      <c r="G170" s="2" t="inlineStr"/>
-      <c r="H170" s="2" t="inlineStr">
+      <c r="G172" s="2" t="inlineStr"/>
+      <c r="H172" s="2" t="inlineStr">
         <is>
           <t>96
  FBA removal and disposal fees will now be charged on a per-unit basis at the time each unit is removed or disposed of.
@@ -8895,39 +9003,39 @@
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="2" t="inlineStr">
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 10:52:42 +0000</t>
         </is>
       </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>Amazon Services Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
+      <c r="F173" s="2" t="inlineStr">
         <is>
           <t>FBA removal and disposal fees to be charged as units are processed</t>
         </is>
       </c>
-      <c r="G171" s="2" t="inlineStr"/>
-      <c r="H171" s="2" t="inlineStr">
+      <c r="G173" s="2" t="inlineStr"/>
+      <c r="H173" s="2" t="inlineStr">
         <is>
           <t>96
  FBA removal and disposal fees will now be charged on a per-unit basis at the time that each unit is removed or disposed of.
@@ -8946,39 +9054,39 @@
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="2" t="inlineStr">
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C172" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D172" s="2" t="inlineStr">
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 09:23:39 +0000</t>
         </is>
       </c>
-      <c r="E172" s="2" t="inlineStr">
+      <c r="E174" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F172" s="2" t="inlineStr">
+      <c r="F174" s="2" t="inlineStr">
         <is>
           <t>Update to FBA item package dimensions</t>
         </is>
       </c>
-      <c r="G172" s="2" t="inlineStr"/>
-      <c r="H172" s="2" t="inlineStr">
+      <c r="G174" s="2" t="inlineStr"/>
+      <c r="H174" s="2" t="inlineStr">
         <is>
           <t>Update to FBA item package dimensions
  96
@@ -8987,39 +9095,39 @@
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="2" t="inlineStr">
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
         <is>
           <t>Fri, 3 Apr 2026 09:46:59 +0000</t>
         </is>
       </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
+      <c r="F175" s="2" t="inlineStr">
         <is>
           <t>C2S2 RXO Partner Broker fees increasing in May 2026</t>
         </is>
       </c>
-      <c r="G173" s="2" t="inlineStr"/>
-      <c r="H173" s="2" t="inlineStr">
+      <c r="G175" s="2" t="inlineStr"/>
+      <c r="H175" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96

--- a/important_mails_2026-05-02.xlsx
+++ b/important_mails_2026-05-02.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H175"/>
+  <dimension ref="A1:H169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -485,7 +485,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>产品链接/合规类</t>
+          <t>付款/资金类</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -500,21 +500,73 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Sat, 2 May 2026 13:15:01 +0000</t>
+          <t>Sat, 2 May 2026 15:23:38 +0000</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+          <t>欧洲亚马逊 Payments &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Submit product safety documentation to reactivate listings</t>
+          <t>跨账户负余额调整</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ 我们已于 五月 2, 2026使用您的 Amazon.es 账户中的可用资金调整了您的 Amazon.de 卖家账户上应付的 €69.53 的负余额。通过登录您的账户并导航至 付款控制面板 ，您可以随时查看您的账户余额。
+有关更多信息，请访问 跨账户负余额调整 。
+诚挚的问候！
+欧洲亚马逊 Payments
+ 报告此电子邮件的问题
+ 如有任何疑问，请访问： 卖家平台
+ 要更改您的电子邮件首选项，请访问： 通知首选项
+ 2026 Amazon, Inc. 或其附属公司。保留所有权利。
+ 欧洲亚马逊 Payments S.C.A.（société en Commandite par actions），是一家在卢森堡注册的股份有限公司，注册号（RCS Luxembourg）B 153 265，公司总部位于 38 avenue J.F.Kennedy, L-1855 Luxembourg。增值税编号为 LU 24448288。
+ 欧洲亚马逊 Payments S.C.A. 由卢森堡金融行业监管委员会授权，并由爱尔兰中央银行对其业务行为规则的遵守情况进行监管。
+ 亚马逊 Payments 是欧洲亚马逊 Payments S.C.A. 的商业名称。
+ 此电子邮件发送自不受监控的电子邮件地址。
+ SPC-EUAmazon-1724035883551525</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 2 May 2026 13:15:01 +0000</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Submit product safety documentation to reactivate listings</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -532,39 +584,39 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 02:13:49 +0000</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -582,39 +634,39 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 15:27:47 +0600</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Amazon Review Deals &lt;amazonreviewsdeals1@gmail.com&gt;</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Amazon Review Rating Deals</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Not getting sales on Amazon? Even after doing everything right? Then this
 message is for you!
@@ -640,40 +692,40 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 03:15:52 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -689,40 +741,40 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 02:15:51 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -738,39 +790,39 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 02:15:45 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -786,39 +838,39 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 01:23:15 +0000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -834,39 +886,39 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 04:46:00 +0000</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -890,39 +942,39 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 07:28:26 +0000</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (5NT+O11io4)</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -942,39 +994,39 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 23:31:40 +0000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -994,39 +1046,39 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:27:01 +0000</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1043,39 +1095,39 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:26:48 +0000</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1095,39 +1147,39 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 17:03:06 +0000</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1147,39 +1199,39 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Sun, 26 Apr 2026 14:08:56 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1196,39 +1248,39 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Sun, 26 Apr 2026 14:08:50 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1248,39 +1300,39 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:19:29 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1298,39 +1350,39 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 12:52:07 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -1346,39 +1398,39 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 02:11:27 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1396,39 +1448,39 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 14:14:16 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1446,39 +1498,39 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 13:03:36 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility 96
  Complete Pan EU enrollment: Add NL products now
@@ -1488,39 +1540,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 09:05:17 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>【请勿回复此日志，如有问题请加入下方邮件中的企微群】
 卖家您好，
@@ -1541,39 +1593,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:13:11 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -1589,39 +1641,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:52:19 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -1640,39 +1692,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 03:13:33 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;merch.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20093870001] Other account issues</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>Hello from Amazon Selling Partner Support,
 My name is Ritam. I am a Live Channel Specialist and I'm contacting you to follow up on your concern regarding the reinstatement of your listing B0FCDRNTT8.
@@ -1683,39 +1735,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 15:09:15 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -1731,39 +1783,39 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:16:19 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -1777,39 +1829,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 02:33:13 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Transparency Invoice/Credit note for 04/2026</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>96
  Dear Customer,
@@ -1827,40 +1879,40 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 02:13:34 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -1876,39 +1928,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 02:13:30 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -1924,39 +1976,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 01:21:43 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -1972,40 +2024,40 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 01:18:50 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -2021,39 +2073,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 21:55:17 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>规划您的 La French Week 促销活动</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -2070,39 +2122,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 21:32:46 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩
 尊敬的卖家，
@@ -2131,39 +2183,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 15:08:42 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -2179,39 +2231,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 14:12:49 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -2225,39 +2277,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 14:07:32 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -2272,39 +2324,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 10:18:53 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -2324,39 +2376,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 20:59:56 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Tus límites de capacidad de Logística de Amazon para mayo</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>96
  Tus límites de capacidad de Logística de Amazon para mayo
@@ -2385,40 +2437,40 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 14:37:52 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Il team di Gestione multicanale &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Aggiornamenti ai costi di Gestione multicanale in vigore dal 29
  maggio 2026</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>96
  Stiamo aggiornando le tariffe di Gestione multicanale per aiutarti a ridurre i costi e investire nella crescita della tua attività.
@@ -2431,39 +2483,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 14:30:37 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>The Multichannel Fulfillment team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>MCF fee updates effective May 29, 2026</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  We’re updating our Multichannel Fulfillment fees to help you reduce your costs so you can invest in growing your business.
@@ -2478,39 +2530,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 14:25:56 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>El Departamento de Logística Multicanal &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Actualización de las tarifas de Logística Multicanal en vigor a partir del 29 de mayo de 2026</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>96
  Vamos a actualizar nuestras tarifas de Logística Multicanal para ayudarte a reducir los costes y así puedas invertir en hacer crecer tu negocio.
@@ -2523,40 +2575,40 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:38:42 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Presenta documentos de cumplimiento normativo del producto para
  evitar que se retiren los listings</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta documentos de cumplimiento normativo del producto para evitar que se retiren los listings
@@ -2571,40 +2623,40 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:25:34 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Documenten over productconformiteit indienen om verwijdering van
  productvermeldingen te voorkomen</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>96
  Documenten over productconformiteit indienen om verwijdering van productvermeldingen te voorkomen
@@ -2618,39 +2670,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:06:50 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Prześlij dokumenty zgodności dotyczące produktu, aby zapobiec usunięciu oferty</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Prześlij dokumenty zgodności dotyczące produktu, aby zapobiec usunięciu oferty
@@ -2664,39 +2716,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:58:32 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Skicka in dokument om produktöverensstämmelse för att undvika att produktposter tas bort</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in dokument om produktöverensstämmelse för att undvika att produktposter tas bort
@@ -2711,39 +2763,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:54:06 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione di conformità dei prodotti per evitare la rimozione delle offerte</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione di conformità dei prodotti per evitare la rimozione delle offerte
@@ -2757,39 +2809,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:50:08 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Soumettez les documents de conformité des produits pour éviter le retrait de la mise en vente</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettez les documents de conformité des produits pour éviter le retrait de la mise en vente
@@ -2804,39 +2856,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 15:58:40 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -2851,39 +2903,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Mon, 27 Apr 2026 05:22:10 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -2902,39 +2954,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Sun, 26 Apr 2026 11:10:42 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -2950,39 +3002,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 00:16:37 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>View your US Q2-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q2-2026
@@ -3012,39 +3064,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 18:05:15 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>提交商品合规文件，以避免商品被移除</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>96
  提交商品合规文件，以避免商品被移除
@@ -3093,39 +3145,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 14:54:23 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $44.85 in an attempt to settle your Amazon seller account balance.
@@ -3141,39 +3193,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 04:59:05 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (26041219YV)</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3193,39 +3245,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 02:11:54 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (W4mGNrNTVu)</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -3251,39 +3303,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 15:50:12 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3301,64 +3353,6 @@
  Copyright 2026 Amazon, Inc, or its affiliates. All rights reserved.
  Amazon.com, 410 Terry Avenue North, Seattle, WA 98109-5210
  SPC-USAmazon-2146248899841341</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 2 Apr 2026 02:11:54 +0000</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>Your FBA removal request is complete (pVfzD86piw)</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>Greetings from Amazon.com
-We thought you'd like to know that we have completed and shipped your removal
-request (pVfzD86piw) to the address you specified before.
-Return Summary:
-Quantity Requested: 3
-Quantity Successfully Shipped: 3
-Quantity Cancelled: 0
-You can track the status of this request by visiting your Seller Account at:
-https://sellercentral.amazon.com/
-For a complete list of inventory being shipped, go to:
-https://sellercentral.amazon.com/gp/orders/fba-order-details.html?orderID=S01-1560397-6680802
-Please note: this email was sent from a notification-only address that
-cannot accept incoming e-mail. Please do not reply to this message.
-Thank you for using Fulfillment by Amazon.
---------------------------------------------------------------------------
-Fulfillment by Amazon, professional packing, shipping and servicing of
-online orders.
---------------------------------------------------------------------------
-Was this email helpful?
- https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
-SPC-USAmazon-1143494293097040</t>
         </is>
       </c>
     </row>
@@ -4011,7 +4005,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>付款/资金类</t>
+          <t>产品链接/合规类</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -4026,70 +4020,21 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Thu, 2 Apr 2026 15:38:29 +0000</t>
+          <t>Fri, 24 Apr 2026 17:15:23 +0000</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>Tu pago está en camino</t>
+          <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr"/>
       <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- ¡Enhorabuena! El pago está de camino y llegará pronto.
- El pago está en camino
-Enhorabuena, Weihai EU. Tu pago está en camino y te llegará en un plazo de tres a cinco días.
-El 04/02/26 15:38 WEST, iniciamos una transferencia a tu método de pago (cuenta bancaria terminado en 229) por un importe de €
- 23,43.
- Si el importe es inferior a lo esperado, ten en cuenta las siguientes preguntas:
- ¿Tienes saldo no disponible en tu cuenta de vendedor? Puede que hayamos reservado algo de dinero para posibles devoluciones, reclamaciones o reversiones de cargo de clientes. En este caso, el saldo de cierre de tu informe de pagos te mostrará el saldo no disponible en reserva.
- ¿Cubren tus ventas las tarifas de Amazon y las devoluciones del periodo de liquidación? El importe del pago refleja las ventas que has hecho y las tarifas de venta aplicadas tanto a dichas ventas como a cualquier promoción o servicio que hayas utilizado. Te recomendamos que revises tu informe de pagos en "Informes" de Seller Central para conocer el saldo de cierre.
-Para más información sobre los informes de pagos en Seller Central, visita nuestro curso oficial.
-Te deseamos un éxi</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 24 Apr 2026 17:15:23 +0000</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>Your Amazon.com Inventory - Action Required</t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -4108,39 +4053,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:15:37 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -4159,39 +4104,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:09:18 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -4210,39 +4155,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Apr 2026 03:03:00 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 You recently received a notice about the removal of your listing(s) for the product(s) listed below.
@@ -4262,39 +4207,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Apr 2026 01:27:00 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;merch.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20061337331] 对危险品分类提出异议</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家/供应商:您好!
 我们了解到您希望重新激活商品 ASIN: B0FCDRNTT8。
@@ -4323,39 +4268,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 10:07:05 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -4373,39 +4318,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:15:48 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4423,39 +4368,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:08:57 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4473,39 +4418,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 06:10:23 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>"compliance-ops-mass-programs@amazon.com" &lt;compliance-ops-mass-programs@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12449434352] 【邀请函】诚邀您参与亚马逊卖家合规策略调研</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>尊敬的销售伙伴，
 您好！
@@ -4519,39 +4464,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 21:09:24 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4569,40 +4514,40 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 14:16:35 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE:
  A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -4619,40 +4564,40 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 09:57:17 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -4669,39 +4614,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 16:06:35 +0800 (GMT+08:00)</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>苏浩然 &lt;suhr@cvc.org.cn&gt;</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Amazon DV TIC</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家，您好。
 我们可以为您提供亚马逊DV验证报告服务。
@@ -4735,39 +4680,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 10:14:18 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -4782,39 +4727,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 03:38:27 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are contacting you to let you know that you could be missing out on sales opportunities because of your incomplete listings.
@@ -4830,39 +4775,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Fri, 17 Apr 2026 11:22:53 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>"pc-eu-sesu-seller-compliance@amazon.com" &lt;pc-eu-sesu-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 11569978862] 【需立即行动】请通过亚马逊认可的TIC服务商完成儿童玩具合规</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 我们紧急通知您，您在【欧洲】站点的部分【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】或【已通过】。
@@ -4886,39 +4831,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Apr 2026 17:53:23 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -4937,39 +4882,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 09:10:03 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -4985,39 +4930,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 07:35:31 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>Seller Assistant now available in the UK</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>Seller Assistant now available in the UK
 [Amazon logo](https://go.amazonsellerservices.com/e/229492/-ld-EMUSSMX-PD25/7z2r9lq/6605548725/h/3xRPn8Yyq31Jz0Gqi8FK51O58vBJkaDT5nhLB1ousbA)
@@ -5029,39 +4974,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 06:23:28 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 You recently received a notice about the removal of your listing(s) for the product(s) listed below.
@@ -5081,39 +5026,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Sun, 12 Apr 2026 09:09:25 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -5131,40 +5076,40 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 15:28:03 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -5182,39 +5127,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 12:03:53 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>Reactivate your EU listings - GPSR compliance required</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Reactivate your EU listings - GPSR compliance required
@@ -5234,39 +5179,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 10:50:30 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>EU and UK Compliance Brief</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe
  96
@@ -5287,39 +5232,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 10:38:53 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>EU and UK Compliance Brief</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe
  96
@@ -5340,40 +5285,40 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 10:23:33 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>The Amazon Europe team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>VAT Calculation Services will calculate VAT by shipment as of June
  1</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>96
  New tax calculation method ensures compliance with European e-invoicing mandates.
@@ -5389,194 +5334,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 2 Apr 2026 04:56:03 +0000</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
-        <is>
-          <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
-        </is>
-      </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
-        <is>
-          <t>【请勿回复】
-尊敬的销售合作伙伴，
-《2025/40包装和包装废弃物法规》（PPWR）为所有欧盟国家引入了新要求，旨在使包装更具可持续性、减少废弃物并支持循环经济。相关要求预计于2026年8月12日起正式生效。
-您需要为每个销售包装及包装产品的欧盟成员国，分别获取一个对应国家的EPR包装注册号。包括您已注册“EPR代付服务”的国家。提交有效的包装EPR注册号（ERN）后，您可继续参与EPR代付服务——由我们负责及时完成您在亚马逊店铺销售的环保款项申报、填报及付款。
-【如何完成合规？】
-1. 为简化法国、意大利和西班牙的EPR包装注册流程并协助您完成注册，我们与服务提供商建立了合作，提供具有竞争力的收费方案：
-• 协助您获取法国、意大利和西班牙的包装注册号
-• 代表您担任授权代表（如适用）
-如需 Evat Master/AVASK联系： 请访问 https://sellercentral-europe.amazon.com/gc/epr-compliance/epr-registration-packaging?ref=121_SET_PPWR 根据步骤1提示选择您的服务提供商，通过卖家平台服务中心表单提交您的联系信息。
-注意：填写注册表时，请务必根据提示完整填写您的信息。填写后我们将与服务提供商共享您的业务信息，服务提供商将在72小时内与您联系，提供更多合规服务信息。
-2. 如果您已注册“EPR代付服务”（法国、意大利、西班牙）且拥有有效注册号：您需要将号码上传到亚马逊平台，但上传时您仍然可以选择继续参与代付服务或退出以便自行管理EPR销售申报环保费用。
-如何操作：请访问： https://sellercentral-europe.amazon.com/gc/epr-compliance/epr-registration-packaging?ref=121_SET_PPWR 根据步骤2提示完成选择。
-3. 此外，您也可以通过以下任一途径搜索并选择服务提供商、授权代表完成EPR所有欧盟国家包装法号码注册：
-1) 亚马逊服务商网络：https://spn.globalsellingcommunity.cn/discover
-2) 卖家服务商城： https://sellercentral-europe.amazon.com/service-hub （包装法服务即将上线）。
-更多详细指导，请参考此合规手册：https://m.media-amazon.com/images/G/01/CN_Compliance_Team/PPWR_Compliance_Guidebook.pdf
-如有疑问，请扫码加入亚马逊卖家合规群：
-https://m.media-amazon.com/images/G/01/CN_Compliance_Team/mass_wecom_yt.jp</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 2 Apr 2026 02:19:17 +0000</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F100" s="2" t="inlineStr">
-        <is>
-          <t>Submit product safety documentation to reactivate listings</t>
-        </is>
-      </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
-        <is>
-          <t>96
- Submit product safety documentation to reactivate listings
- Hello Weihai EU,
- Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listings?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
--
- If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 2 Apr 2026 02:18:50 +0000</t>
-        </is>
-      </c>
-      <c r="E101" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F101" s="2" t="inlineStr">
-        <is>
-          <t>Submit product safety documentation to reactivate listings</t>
-        </is>
-      </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
-        <is>
-          <t>96
- Submit product safety documentation to reactivate listings
- Hello Weihai EU,
- Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listings?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
--
- If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Apr 2026 05:38:32 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -5597,39 +5387,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:19:11 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -5647,40 +5437,40 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:18:24 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om de deactivering van de
  productvermelding te voorkomen</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -5698,39 +5488,39 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:15:32 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -5747,39 +5537,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:12:50 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -5797,40 +5587,40 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:12:30 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per evitare la
  disattivazione dell'offerta</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -5848,39 +5638,39 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:09:22 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour éviter la désactivation des mises en vente</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>96
  Bonjour Weihai EU,
@@ -5898,39 +5688,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 00:31:36 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>规划您的 La French Week 促销活动</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -5947,39 +5737,39 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Apr 2026 15:00:54 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5994,39 +5784,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Apr 2026 07:42:42 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Act today &amp; improve Sales on Excess Inventory</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6045,39 +5835,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:32:20 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>Prime Day：立即提报您的促销</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>Prime Day（日期待公布）：立即提报您的促销
 尊敬的卖家，
@@ -6095,39 +5885,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:19:47 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以重新启售商品</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>96
  提交商品安全文件以重新启售商品
@@ -6166,39 +5956,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:17:42 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -6214,40 +6004,40 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:17:14 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -6263,39 +6053,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:13:36 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -6311,39 +6101,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:13:34 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -6357,40 +6147,40 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:11:30 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -6406,39 +6196,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:09:39 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -6454,39 +6244,39 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 05:22:42 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -6507,39 +6297,39 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 15:14:51 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -6554,39 +6344,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Fri, 17 Apr 2026 09:39:52 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>Verify your primary operating address for tax purposes</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Amazon Services
  Verify your primary operating address for tax purposes
@@ -6603,39 +6393,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Apr 2026 15:10:49 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>[Formal Notice – Immediate Action Required] Review and certify your business information within 10 days to avoid account deactivation</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -6649,39 +6439,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 17:59:02 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>Amazon Verkaeuferservice &lt;merch.service05@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12354633592] 其他账户问题</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>尊敬的销售伙伴：
 您好！
@@ -6700,40 +6490,40 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 17:22:14 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>Amazon Product Support Team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>Reduce Returns &amp; Boost Customer Satisfaction - Enrol in Amazon
  Product Support</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>96
  Enrol now into Amazon Product Support !
@@ -6747,40 +6537,40 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 13:44:27 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Reactiva tus listings en la UE: se requiere el cumplimiento del
  Reglamento relativo a la seguridad general de los productos</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>96
  Reactiva tus listings en la UE: se requiere el cumplimiento del Reglamento relativo a la seguridad general de los productos
@@ -6798,39 +6588,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 01:52:13 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Re: 🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 Just a short follow-up regarding the [Vergleich.org](http://Vergleich.org)
@@ -6863,39 +6653,39 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 17:17:52 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Introducing Global Warehousing &amp; Distribution</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>96
  Store inventory at origin in China with lower costs and faster speeds.
@@ -6910,39 +6700,39 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 16:27:24 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 3/2026 (Votre Facture Expédié Par Amazon Amazon.ca pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -6961,39 +6751,39 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 11:49:51 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>96
  Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti
@@ -7012,39 +6802,39 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 10:53:45 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>Las tarifas por puesta de inventario a disposición de Amazon y retirada de Logística de Amazon se cobrarán a medida que se procesen las unidades</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>96
  Las tarifas por retirada y puesta de inventario a disposición de Amazon de Logística de Amazon se cobrarán ahora por unidad en el momento en que cada unidad se retire o se ponga a nuestra disposición.
@@ -7056,39 +6846,39 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 09:19:33 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>Opłaty za usunięcie i likwidację zapasów FBA naliczane podczas przetwarzania jednostek</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>96
  Opłaty za wycofanie i usunięcie zapasów w ramach FBA będą teraz pobierane od każdej jednostki w momencie jej wycofania lub usunięcia.
@@ -7104,39 +6894,39 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 08:46:52 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>Addebito delle tariffe di rimozione e per reimpiego quando le unità vengono elaborate</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>96
  Le tariffe per gli ordini di rimozione e di reimpiego di inventario di Logistica di Amazon verranno ora addebitate per unità ogni volta che un'unità viene rimossa o destinata ad altro uso.
@@ -7148,39 +6938,39 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 15:00:43 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -7195,39 +6985,39 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 01:13:24 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Verkäufer von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Verkäufer für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -7239,39 +7029,39 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 00:28:23 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>Je Creditnota Verkoper Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Creditnota Verkoper voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -7283,39 +7073,39 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 23:40:40 +0000</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -7327,39 +7117,39 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:17:10 +0000</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -7371,39 +7161,39 @@
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:08:24 +0000</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -7415,39 +7205,39 @@
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:03:23 +0000</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 3/2026</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -7459,39 +7249,39 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 21:18:12 +0000</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -7503,39 +7293,39 @@
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:40:48 +0000</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 3/2026</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 3/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -7547,39 +7337,39 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:23:05 +0000</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -7591,39 +7381,39 @@
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:10:52 +0000</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 3/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -7642,39 +7432,39 @@
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:00:59 +0000</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -7686,39 +7476,39 @@
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 19:23:08 +0000</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Selbstfakturierung AGL von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Selbstfakturierung AGL für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -7730,39 +7520,39 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 18:31:47 +0000</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 3/2026</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic AGL Merchant Self-Billing Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -7774,39 +7564,39 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:54:15 +0000</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Säljare Amazon.se för 3/2026</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Säljare för månaden 3/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -7818,39 +7608,39 @@
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:52:00 +0000</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -7862,39 +7652,39 @@
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:39:20 +0000</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 3/2026</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -7906,39 +7696,39 @@
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:07:04 +0000</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 3/2026</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr"/>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 3/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -7950,39 +7740,39 @@
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:06:30 +0000</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 3/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -8001,39 +7791,39 @@
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 15:55:59 +0000</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr"/>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -8045,40 +7835,40 @@
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 15:00:18 +0000</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.com.be voor 3/2026 (Votre Facture
  Vendeur Amazon.com.be pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr"/>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -8097,39 +7887,39 @@
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 14:50:20 +0000</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Verkäufer von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr"/>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Verkäufer für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -8141,39 +7931,39 @@
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 14:43:40 +0000</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.sa Merchant Invoice for 3/2026 (Amazon.sa فاتورة ضريبة القيمة المضافة (VAT) الخاصة بالتاجر الخاصة بك لشهر 3/2026)</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr"/>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -8192,39 +7982,39 @@
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Mon, 06 Apr 2026 01:10:45 +0000</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Re: 🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr"/>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 I wanted to briefly follow up regarding the Vergleich.org award for your
@@ -8256,39 +8046,39 @@
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 15:20:39 +0000</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12317833332] 其他账户问题</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr"/>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家/供应商：您好！
 关于您 ASIN B0CSGBZG8W 购物车的问题，经过审核，我们发现该商品的价格不符合成为推荐商品的条件，因为它似乎过高。
@@ -8315,39 +8105,39 @@
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 09:59:13 +0000</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>&lt;p&gt;Grazie per aver creato un nuovo caso: -- 12317833332&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr"/>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>La ringraziamo per aver contattato il Supporto al venditore di Amazon.
 Abbiamo aperto un caso riguardo al suo problema. Un membro del nostro team la contatterà appena possibile. Rispondiamo alla maggior parte delle e-mail entro 12 ore.
@@ -8359,123 +8149,39 @@
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 2 Apr 2026 14:57:25 +0000</t>
-        </is>
-      </c>
-      <c r="E160" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F160" s="2" t="inlineStr">
-        <is>
-          <t>Recargo relacionado con combustible y gastos de logística: Logística de Amazon y Logística Multicanal en la UE</t>
-        </is>
-      </c>
-      <c r="G160" s="2" t="inlineStr"/>
-      <c r="H160" s="2" t="inlineStr">
-        <is>
-          <t>96
- A partir del 17 de abril de 2026, se aplicará un recargo por combustible y gastos de logística del 1,5 % a las tarifas de gestión logística de Logística de Amazon. En el caso de Logística Multicanal, este recargo entrará en vigor el 2 de mayo de 2026.
- Hola:
- El aumento de los costes del combustible y logística ha incrementado los gastos operativos en todo el sector. Hasta ahora, hemos podido asimilar este aumento de costes. Sin embargo, al igual que otros transportistas importantes, cuando los costes se mantienen altos, aplicamos recargos temporales a nuestras tarifas de gestión logística para recuperar una parte de estos aumentos de costes.
- A partir del 17 de abril de 2026, se aplicará un recargo por combustible y gastos de logística del 1,5 % a las tarifas de gestión logística de Logística de Amazon del Reino Unido, Francia, Alemania, Italia, España, Polonia, Suecia, Países Bajos, Irlanda y Bélgica. A partir del 2 de mayo de 2026, este mismo recargo entrará en vigor para el servicio de Logística Multicanal en el Reino Unido, Francia, Alemania, Italia y España. Gracias al trabajo que hemos llevado a cabo juntos para reducir los costes, este recargo es considerablemente infer</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 2 Apr 2026 14:01:37 +0000</t>
-        </is>
-      </c>
-      <c r="E161" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F161" s="2" t="inlineStr">
-        <is>
-          <t>Dopłata z tytułu kosztów paliwa i logistyki: usługi FBA i MFC w UE</t>
-        </is>
-      </c>
-      <c r="G161" s="2" t="inlineStr"/>
-      <c r="H161" s="2" t="inlineStr">
-        <is>
-          <t>96
- Od 17 kwietnia 2026 r. do opłat za realizację w programie „Realizacja przez Amazon” (FBA) zaczynamy doliczać dopłatę w wysokości 1,5% z tytułu kosztów paliwa i logistyki. W przypadku usługi „Realizacja wielokanałowa” (MCF) dopłata ta będzie miała zastosowanie od 2 maja 2026 r.
- Dzień dobry,
- wzrost cen paliwa i transportu przyczynił się do zwiększenia kosztów operacyjnych w całej branży. Do tej pory pokrywaliśmy te zwiększone koszty. Jednak, ponieważ wzrost kosztów się utrzymuje, wprowadzamy tymczasowe dopłaty do opłat za realizację. Celem jest odzyskanie części zwiększonych kosztów rzeczywistych, które ponosimy. Podobne działania podejmują inni najważniejsi przewoźnicy.
- Od 17 kwietnia 2026 r. do opłat za realizację w programie „Realizacja przez Amazon” (FBA) w Zjednoczonym Królestwie, Francji, Niemczech, Włoszech, Hiszpanii, Polsce, Szwecji, Holandii, Irlandii i Belgii zaczynamy doliczać dopłatę w wysokości 1,5% z tytułu kosztów paliwa i logistyki . W przypadku usługi „Realizacja wielokanałowa” (MCF) w Zjednoczonym Królestwie, Francji, Niemczech, Włoszech i Hiszpanii dopłata ta będzie miała zastosowanie od 2 maja 2026 r. Dzięki wspólnym wysiłkom, jakie podjęliśmy już wcześnie</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Apr 2026 04:25:43 +0000</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F162" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G162" s="2" t="inlineStr"/>
-      <c r="H162" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -8499,39 +8205,39 @@
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Apr 2026 03:35:07 +0000</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F163" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-05-07</t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr"/>
-      <c r="H163" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -8552,39 +8258,39 @@
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 04:00:50 +0000</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F164" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-30</t>
         </is>
       </c>
-      <c r="G164" s="2" t="inlineStr"/>
-      <c r="H164" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -8606,39 +8312,39 @@
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 03:30:46 +0000</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F165" s="2" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G165" s="2" t="inlineStr"/>
-      <c r="H165" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr"/>
+      <c r="H159" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -8661,39 +8367,39 @@
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 18:58:06 +0000</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F166" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-23</t>
         </is>
       </c>
-      <c r="G166" s="2" t="inlineStr"/>
-      <c r="H166" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -8714,39 +8420,39 @@
         </is>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 18:27:29 +0000</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F167" s="2" t="inlineStr">
+      <c r="F161" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G167" s="2" t="inlineStr"/>
-      <c r="H167" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr"/>
+      <c r="H161" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -8769,39 +8475,39 @@
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="2" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D168" s="2" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:48:38 +0000</t>
         </is>
       </c>
-      <c r="E168" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F168" s="2" t="inlineStr">
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t>Remove aged, stranded and unfulfillable inventory by April 30</t>
         </is>
       </c>
-      <c r="G168" s="2" t="inlineStr"/>
-      <c r="H168" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr"/>
+      <c r="H162" s="2" t="inlineStr">
         <is>
           <t>96
  Take action now to avoid automatic removal of your Fulfilment by Amazon inventory.
@@ -8814,39 +8520,39 @@
         </is>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 11:41:39 +0800 (GMT+08:00)</t>
         </is>
       </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t>GTTC国际业务部玩具组 &lt;gttctoy@cngttc.cn&gt;</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
+      <c r="F163" s="2" t="inlineStr">
         <is>
           <t>AMAZON DV TIC TRF ID--Top urgently</t>
         </is>
       </c>
-      <c r="G169" s="2" t="inlineStr"/>
-      <c r="H169" s="2" t="inlineStr">
+      <c r="G163" s="2" t="inlineStr"/>
+      <c r="H163" s="2" t="inlineStr">
         <is>
           <t>Dear Vendor,        Some of your TR numbers on Amazon have been pending in our backend for a long time without timely processing. We plan to automatically clear all unresponded TR numbers in our system two days later.
 If you have any TR numbers that require sample submission for testing, please reply to this email and send us the corresponding TR numbers within two days, and contact our relevant customer service within one week to arrange sample submission.
@@ -8855,39 +8561,39 @@
         </is>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" s="2" t="inlineStr">
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C170" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D170" s="2" t="inlineStr">
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>Fri, 17 Apr 2026 02:18:44 +0000</t>
         </is>
       </c>
-      <c r="E170" s="2" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F170" s="2" t="inlineStr">
+      <c r="F164" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G170" s="2" t="inlineStr"/>
-      <c r="H170" s="2" t="inlineStr">
+      <c r="G164" s="2" t="inlineStr"/>
+      <c r="H164" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
@@ -8903,39 +8609,39 @@
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="2" t="inlineStr">
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 14:20:37 +0000</t>
         </is>
       </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
+      <c r="F165" s="2" t="inlineStr">
         <is>
           <t>Get discounts up to €500 per shipment by expanding to Europe!</t>
         </is>
       </c>
-      <c r="G171" s="2" t="inlineStr"/>
-      <c r="H171" s="2" t="inlineStr">
+      <c r="G165" s="2" t="inlineStr"/>
+      <c r="H165" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/-logo/7z2qvdy/6598918207/h/oQJ3hcZAc232rnIjbHrMLH2dvtBVfEq_dAzSA60S8Es)
 C2S2 PCP Pallet Limited Time Promotion
@@ -8951,39 +8657,39 @@
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="2" t="inlineStr">
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C172" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D172" s="2" t="inlineStr">
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 11:27:28 +0000</t>
         </is>
       </c>
-      <c r="E172" s="2" t="inlineStr">
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F172" s="2" t="inlineStr">
+      <c r="F166" s="2" t="inlineStr">
         <is>
           <t>FBA removal and disposal fees to be charged as units are processed</t>
         </is>
       </c>
-      <c r="G172" s="2" t="inlineStr"/>
-      <c r="H172" s="2" t="inlineStr">
+      <c r="G166" s="2" t="inlineStr"/>
+      <c r="H166" s="2" t="inlineStr">
         <is>
           <t>96
  FBA removal and disposal fees will now be charged on a per-unit basis at the time each unit is removed or disposed of.
@@ -9003,39 +8709,39 @@
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="2" t="inlineStr">
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 10:52:42 +0000</t>
         </is>
       </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="E167" s="2" t="inlineStr">
         <is>
           <t>Amazon Services Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
+      <c r="F167" s="2" t="inlineStr">
         <is>
           <t>FBA removal and disposal fees to be charged as units are processed</t>
         </is>
       </c>
-      <c r="G173" s="2" t="inlineStr"/>
-      <c r="H173" s="2" t="inlineStr">
+      <c r="G167" s="2" t="inlineStr"/>
+      <c r="H167" s="2" t="inlineStr">
         <is>
           <t>96
  FBA removal and disposal fees will now be charged on a per-unit basis at the time that each unit is removed or disposed of.
@@ -9054,39 +8760,39 @@
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="2" t="inlineStr">
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B174" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C174" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D174" s="2" t="inlineStr">
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 09:23:39 +0000</t>
         </is>
       </c>
-      <c r="E174" s="2" t="inlineStr">
+      <c r="E168" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F174" s="2" t="inlineStr">
+      <c r="F168" s="2" t="inlineStr">
         <is>
           <t>Update to FBA item package dimensions</t>
         </is>
       </c>
-      <c r="G174" s="2" t="inlineStr"/>
-      <c r="H174" s="2" t="inlineStr">
+      <c r="G168" s="2" t="inlineStr"/>
+      <c r="H168" s="2" t="inlineStr">
         <is>
           <t>Update to FBA item package dimensions
  96
@@ -9095,39 +8801,39 @@
         </is>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="2" t="inlineStr">
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B175" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr">
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
         <is>
           <t>Fri, 3 Apr 2026 09:46:59 +0000</t>
         </is>
       </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
         <is>
           <t>C2S2 RXO Partner Broker fees increasing in May 2026</t>
         </is>
       </c>
-      <c r="G175" s="2" t="inlineStr"/>
-      <c r="H175" s="2" t="inlineStr">
+      <c r="G169" s="2" t="inlineStr"/>
+      <c r="H169" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
